--- a/p6_deployment/data/france/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/france/data_preparation/df_filled.xlsx
@@ -697,76 +697,76 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>27.12517482517482</v>
+        <v>27.33806818181818</v>
       </c>
       <c r="Q2" t="n">
-        <v>183.6510489510489</v>
+        <v>183.2903409090909</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>69.21328671328672</v>
+        <v>69.21534090909091</v>
       </c>
       <c r="T2" t="n">
-        <v>1694458.041958042</v>
+        <v>1655241.477272728</v>
       </c>
       <c r="U2" t="n">
-        <v>72.34055944055945</v>
+        <v>72.13806818181817</v>
       </c>
       <c r="V2" t="n">
-        <v>26.30769230769231</v>
+        <v>26.0969696969697</v>
       </c>
       <c r="W2" t="n">
-        <v>180.1748251748251</v>
+        <v>180.4</v>
       </c>
       <c r="X2" t="n">
-        <v>1.412587412587413</v>
+        <v>1.412121212121213</v>
       </c>
       <c r="Y2" t="n">
-        <v>77.006993006993</v>
+        <v>76.9939393939394</v>
       </c>
       <c r="Z2" t="n">
-        <v>13332517.48251748</v>
+        <v>13494242.42424243</v>
       </c>
       <c r="AA2" t="n">
-        <v>79.66433566433565</v>
+        <v>79.85454545454546</v>
       </c>
       <c r="AB2" t="n">
-        <v>24.23724992955762</v>
+        <v>24.19276556776557</v>
       </c>
       <c r="AC2" t="n">
-        <v>182.619752042829</v>
+        <v>182.9535485347986</v>
       </c>
       <c r="AD2" t="n">
         <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>64.93885601577909</v>
+        <v>64.95448717948719</v>
       </c>
       <c r="AF2" t="n">
-        <v>1088338.264299803</v>
+        <v>1100629.006410256</v>
       </c>
       <c r="AG2" t="n">
-        <v>70.93857424626655</v>
+        <v>71.01467490842491</v>
       </c>
       <c r="AH2" t="n">
-        <v>26.32860195360195</v>
+        <v>26.50701058201058</v>
       </c>
       <c r="AI2" t="n">
-        <v>178.903083028083</v>
+        <v>178.6937830687831</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.374847374847375</v>
+        <v>1.369312169312169</v>
       </c>
       <c r="AK2" t="n">
-        <v>74.18543956043956</v>
+        <v>74.1755291005291</v>
       </c>
       <c r="AL2" t="n">
-        <v>6735462.454212455</v>
+        <v>6571474.867724868</v>
       </c>
       <c r="AM2" t="n">
-        <v>77.27899877899878</v>
+        <v>77.13068783068783</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
@@ -842,76 +842,76 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>25.8041958041958</v>
+        <v>25.89204545454546</v>
       </c>
       <c r="Q3" t="n">
-        <v>181.4265734265734</v>
+        <v>181.3295454545454</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>68.3986013986014</v>
+        <v>68.49431818181819</v>
       </c>
       <c r="T3" t="n">
-        <v>1671853.146853147</v>
+        <v>1682244.318181818</v>
       </c>
       <c r="U3" t="n">
-        <v>71.35664335664336</v>
+        <v>71.33522727272728</v>
       </c>
       <c r="V3" t="n">
-        <v>23.55944055944056</v>
+        <v>23.6524064171123</v>
       </c>
       <c r="W3" t="n">
-        <v>183.4125874125874</v>
+        <v>183.3689839572192</v>
       </c>
       <c r="X3" t="n">
-        <v>1.321678321678322</v>
+        <v>1.32620320855615</v>
       </c>
       <c r="Y3" t="n">
-        <v>75.26573426573427</v>
+        <v>75.24064171122994</v>
       </c>
       <c r="Z3" t="n">
-        <v>12688811.18881119</v>
+        <v>12514973.26203208</v>
       </c>
       <c r="AA3" t="n">
-        <v>79.93706293706295</v>
+        <v>79.89304812834224</v>
       </c>
       <c r="AB3" t="n">
-        <v>23.26073926073926</v>
+        <v>23.14935064935065</v>
       </c>
       <c r="AC3" t="n">
-        <v>180.8816183816184</v>
+        <v>181.0645292207792</v>
       </c>
       <c r="AD3" t="n">
         <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>65.15734265734265</v>
+        <v>65.02962662337663</v>
       </c>
       <c r="AF3" t="n">
-        <v>1375000</v>
+        <v>1364285.714285714</v>
       </c>
       <c r="AG3" t="n">
-        <v>71.82617382617383</v>
+        <v>71.91233766233766</v>
       </c>
       <c r="AH3" t="n">
-        <v>23.79526540710751</v>
+        <v>23.68470809376382</v>
       </c>
       <c r="AI3" t="n">
-        <v>180.4569034766403</v>
+        <v>180.2043220797091</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.281007004691215</v>
+        <v>1.248384441495897</v>
       </c>
       <c r="AK3" t="n">
-        <v>73.28030814215025</v>
+        <v>73.14841024128951</v>
       </c>
       <c r="AL3" t="n">
-        <v>6789538.750722962</v>
+        <v>6588942.331318492</v>
       </c>
       <c r="AM3" t="n">
-        <v>78.24195103142472</v>
+        <v>78.19739299228463</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -987,76 +987,76 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>26.38461538461538</v>
+        <v>26.35227272727273</v>
       </c>
       <c r="Q4" t="n">
-        <v>181.7902097902098</v>
+        <v>181.7045454545455</v>
       </c>
       <c r="R4" t="n">
-        <v>1.307692307692308</v>
+        <v>1.301136363636364</v>
       </c>
       <c r="S4" t="n">
-        <v>75.01398601398601</v>
+        <v>74.93181818181817</v>
       </c>
       <c r="T4" t="n">
-        <v>7221678.321678321</v>
+        <v>7138068.181818182</v>
       </c>
       <c r="U4" t="n">
-        <v>77.33566433566433</v>
+        <v>77.25568181818181</v>
       </c>
       <c r="V4" t="n">
-        <v>26.71118881118881</v>
+        <v>26.55090909090909</v>
       </c>
       <c r="W4" t="n">
-        <v>183.5762237762238</v>
+        <v>183.569696969697</v>
       </c>
       <c r="X4" t="n">
-        <v>1.676923076923077</v>
+        <v>1.669090909090909</v>
       </c>
       <c r="Y4" t="n">
-        <v>77.22027972027972</v>
+        <v>77.11999999999999</v>
       </c>
       <c r="Z4" t="n">
-        <v>12516643.35664336</v>
+        <v>12317454.54545454</v>
       </c>
       <c r="AA4" t="n">
-        <v>79.34195804195805</v>
+        <v>79.40363636363637</v>
       </c>
       <c r="AB4" t="n">
-        <v>23.98910256410257</v>
+        <v>23.87743055555556</v>
       </c>
       <c r="AC4" t="n">
-        <v>179.9974358974359</v>
+        <v>179.8616319444445</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.131440781440781</v>
+        <v>1.143253968253968</v>
       </c>
       <c r="AE4" t="n">
-        <v>69.5324481074481</v>
+        <v>69.12792658730157</v>
       </c>
       <c r="AF4" t="n">
-        <v>3575399.114774115</v>
+        <v>3391687.12797619</v>
       </c>
       <c r="AG4" t="n">
-        <v>74.19899267399268</v>
+        <v>74.08876488095238</v>
       </c>
       <c r="AH4" t="n">
-        <v>24.80775704343815</v>
+        <v>24.74450054875751</v>
       </c>
       <c r="AI4" t="n">
-        <v>184.2495079138268</v>
+        <v>184.1523513030943</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.215621538763954</v>
+        <v>1.195205333595427</v>
       </c>
       <c r="AK4" t="n">
-        <v>74.49706524985162</v>
+        <v>74.1863454387603</v>
       </c>
       <c r="AL4" t="n">
-        <v>8642168.675837407</v>
+        <v>8210018.407947974</v>
       </c>
       <c r="AM4" t="n">
-        <v>78.13239972102201</v>
+        <v>77.8814130915524</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
@@ -1128,76 +1128,76 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>25.52121212121212</v>
+        <v>25.36590909090909</v>
       </c>
       <c r="Q5" t="n">
-        <v>186.0674242424243</v>
+        <v>185.7704545454546</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>71.65227272727272</v>
+        <v>71.50170454545454</v>
       </c>
       <c r="T5" t="n">
-        <v>3052500</v>
+        <v>3006875</v>
       </c>
       <c r="U5" t="n">
-        <v>74.94015151515153</v>
+        <v>74.89318181818183</v>
       </c>
       <c r="V5" t="n">
-        <v>24.17338772338773</v>
+        <v>24.22017231134878</v>
       </c>
       <c r="W5" t="n">
-        <v>183.2950660450661</v>
+        <v>183.4426322043969</v>
       </c>
       <c r="X5" t="n">
-        <v>2.368181818181818</v>
+        <v>2.365210932857991</v>
       </c>
       <c r="Y5" t="n">
-        <v>81.51592851592851</v>
+        <v>81.60564468211527</v>
       </c>
       <c r="Z5" t="n">
-        <v>45698076.92307692</v>
+        <v>45499509.80392157</v>
       </c>
       <c r="AA5" t="n">
-        <v>85.44662004662004</v>
+        <v>85.4336898395722</v>
       </c>
       <c r="AB5" t="n">
-        <v>24.92670807453416</v>
+        <v>24.99190605590062</v>
       </c>
       <c r="AC5" t="n">
-        <v>181.4853433402346</v>
+        <v>181.4308477829538</v>
       </c>
       <c r="AD5" t="n">
         <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>68.81062801932367</v>
+        <v>68.52984601449276</v>
       </c>
       <c r="AF5" t="n">
-        <v>2036459.483551875</v>
+        <v>1906706.591830573</v>
       </c>
       <c r="AG5" t="n">
-        <v>73.00268000920175</v>
+        <v>72.81624611801243</v>
       </c>
       <c r="AH5" t="n">
-        <v>24.41857597424935</v>
+        <v>24.33985321275324</v>
       </c>
       <c r="AI5" t="n">
-        <v>183.7611940390191</v>
+        <v>183.4787622112557</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.199077882615035</v>
+        <v>2.188181787026907</v>
       </c>
       <c r="AK5" t="n">
-        <v>78.89121521123069</v>
+        <v>78.73178644495655</v>
       </c>
       <c r="AL5" t="n">
-        <v>33279777.20035383</v>
+        <v>33333094.78223422</v>
       </c>
       <c r="AM5" t="n">
-        <v>83.62849464347143</v>
+        <v>83.7123453952218</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1273,76 +1273,76 @@
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>24.57770007770008</v>
+        <v>24.65347222222222</v>
       </c>
       <c r="Q6" t="n">
-        <v>182.4131313131313</v>
+        <v>182.5606691919192</v>
       </c>
       <c r="R6" t="n">
-        <v>1.586635586635587</v>
+        <v>1.606186868686869</v>
       </c>
       <c r="S6" t="n">
-        <v>76.97746697746699</v>
+        <v>76.99135101010101</v>
       </c>
       <c r="T6" t="n">
-        <v>15304856.25485626</v>
+        <v>15180366.16161616</v>
       </c>
       <c r="U6" t="n">
-        <v>81.43209013209012</v>
+        <v>81.32891414141415</v>
       </c>
       <c r="V6" t="n">
-        <v>25.65909090909091</v>
+        <v>25.78086124401914</v>
       </c>
       <c r="W6" t="n">
-        <v>181.5295454545455</v>
+        <v>181.321052631579</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>70.43977272727273</v>
+        <v>70.50382775119617</v>
       </c>
       <c r="Z6" t="n">
-        <v>2264829.545454545</v>
+        <v>2267057.416267943</v>
       </c>
       <c r="AA6" t="n">
-        <v>73.82727272727273</v>
+        <v>73.78229665071771</v>
       </c>
       <c r="AB6" t="n">
-        <v>21.94877652017745</v>
+        <v>21.65601148354079</v>
       </c>
       <c r="AC6" t="n">
-        <v>181.3824099017598</v>
+        <v>181.1161111813146</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25402275742833</v>
+        <v>1.199589309407974</v>
       </c>
       <c r="AE6" t="n">
-        <v>73.88017051318135</v>
+        <v>73.49054213790779</v>
       </c>
       <c r="AF6" t="n">
-        <v>10179066.04747162</v>
+        <v>9508926.044101851</v>
       </c>
       <c r="AG6" t="n">
-        <v>81.50556722689076</v>
+        <v>81.62886404561824</v>
       </c>
       <c r="AH6" t="n">
-        <v>24.65115786990787</v>
+        <v>24.47315549947129</v>
       </c>
       <c r="AI6" t="n">
-        <v>180.0623820623821</v>
+        <v>180.3457653457653</v>
       </c>
       <c r="AJ6" t="n">
         <v>1</v>
       </c>
       <c r="AK6" t="n">
-        <v>68.57267385392385</v>
+        <v>68.51232685443212</v>
       </c>
       <c r="AL6" t="n">
-        <v>1905206.859113109</v>
+        <v>1912655.4001554</v>
       </c>
       <c r="AM6" t="n">
-        <v>73.7708923021423</v>
+        <v>73.88977396872133</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
@@ -1422,58 +1422,58 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>25.4013986013986</v>
+        <v>25.45681818181818</v>
       </c>
       <c r="Q7" t="n">
-        <v>181.4188811188811</v>
+        <v>181.4426136363637</v>
       </c>
       <c r="R7" t="n">
-        <v>1.346853146853147</v>
+        <v>1.355681818181818</v>
       </c>
       <c r="S7" t="n">
-        <v>73.28391608391608</v>
+        <v>73.2590909090909</v>
       </c>
       <c r="T7" t="n">
-        <v>5451888.111888112</v>
+        <v>5430227.272727272</v>
       </c>
       <c r="U7" t="n">
-        <v>77.5804195804196</v>
+        <v>77.52840909090909</v>
       </c>
       <c r="V7" t="n">
-        <v>22.38023088023088</v>
+        <v>22.37783719548426</v>
       </c>
       <c r="W7" t="n">
-        <v>183.37113997114</v>
+        <v>183.664468211527</v>
       </c>
       <c r="X7" t="n">
-        <v>1.205483405483406</v>
+        <v>1.19863339275104</v>
       </c>
       <c r="Y7" t="n">
-        <v>71.60937950937952</v>
+        <v>71.73713606654783</v>
       </c>
       <c r="Z7" t="n">
-        <v>4571536.796536797</v>
+        <v>4693030.303030304</v>
       </c>
       <c r="AA7" t="n">
-        <v>79.205772005772</v>
+        <v>79.22828282828283</v>
       </c>
       <c r="AB7" t="n">
-        <v>23.87805913892871</v>
+        <v>23.80568495514148</v>
       </c>
       <c r="AC7" t="n">
-        <v>181.6384336677815</v>
+        <v>181.5474971963423</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.137841747624356</v>
+        <v>1.145726578674948</v>
       </c>
       <c r="AE7" t="n">
-        <v>70.65226017943408</v>
+        <v>70.33750107832988</v>
       </c>
       <c r="AF7" t="n">
-        <v>3462888.331475288</v>
+        <v>3326543.1978951</v>
       </c>
       <c r="AG7" t="n">
-        <v>76.31385836385836</v>
+        <v>76.11016865079365</v>
       </c>
       <c r="AH7" t="n">
         <v>23.51894578344158</v>
@@ -1567,76 +1567,76 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>25.68737373737374</v>
+        <v>25.81239316239316</v>
       </c>
       <c r="Q8" t="n">
-        <v>182.5414141414141</v>
+        <v>182.642735042735</v>
       </c>
       <c r="R8" t="n">
-        <v>1.23459595959596</v>
+        <v>1.236965811965812</v>
       </c>
       <c r="S8" t="n">
-        <v>74.51843434343435</v>
+        <v>74.57713675213675</v>
       </c>
       <c r="T8" t="n">
-        <v>7733478.535353536</v>
+        <v>7714481.837606838</v>
       </c>
       <c r="U8" t="n">
-        <v>78.77449494949495</v>
+        <v>78.6707264957265</v>
       </c>
       <c r="V8" t="n">
-        <v>23.97878787878788</v>
+        <v>24.14545454545454</v>
       </c>
       <c r="W8" t="n">
-        <v>180.6643939393939</v>
+        <v>180.5926136363636</v>
       </c>
       <c r="X8" t="n">
-        <v>1.453030303030303</v>
+        <v>1.466477272727273</v>
       </c>
       <c r="Y8" t="n">
-        <v>76.57121212121211</v>
+        <v>76.64204545454545</v>
       </c>
       <c r="Z8" t="n">
-        <v>13362121.21212121</v>
+        <v>13325000</v>
       </c>
       <c r="AA8" t="n">
-        <v>81.50378787878789</v>
+        <v>81.34488636363636</v>
       </c>
       <c r="AB8" t="n">
-        <v>22.65661911188227</v>
+        <v>22.59129211918685</v>
       </c>
       <c r="AC8" t="n">
-        <v>183.4048454469507</v>
+        <v>183.5230882762462</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.079292783240152</v>
+        <v>1.068720412141465</v>
       </c>
       <c r="AE8" t="n">
-        <v>69.17210494184178</v>
+        <v>69.00193539404066</v>
       </c>
       <c r="AF8" t="n">
-        <v>3780689.905854379</v>
+        <v>3671667.362851573</v>
       </c>
       <c r="AG8" t="n">
-        <v>77.49829702461281</v>
+        <v>77.42074631022</v>
       </c>
       <c r="AH8" t="n">
-        <v>25.61708196773986</v>
+        <v>25.54852576151918</v>
       </c>
       <c r="AI8" t="n">
-        <v>181.039393756828</v>
+        <v>181.3932357938115</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.190370959449907</v>
+        <v>1.197837743396954</v>
       </c>
       <c r="AK8" t="n">
-        <v>72.39263141828931</v>
+        <v>72.1042949922884</v>
       </c>
       <c r="AL8" t="n">
-        <v>5764891.244537626</v>
+        <v>5491748.790546076</v>
       </c>
       <c r="AM8" t="n">
-        <v>77.27477066062592</v>
+        <v>77.23226847165992</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
@@ -1712,76 +1712,76 @@
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>24.43636363636363</v>
+        <v>24.40909090909091</v>
       </c>
       <c r="Q9" t="n">
-        <v>181.6666666666667</v>
+        <v>181.6010101010101</v>
       </c>
       <c r="R9" t="n">
-        <v>1.684848484848484</v>
+        <v>1.681818181818181</v>
       </c>
       <c r="S9" t="n">
-        <v>75.81212121212121</v>
+        <v>75.80303030303031</v>
       </c>
       <c r="T9" t="n">
-        <v>10506666.66666666</v>
+        <v>10589898.98989899</v>
       </c>
       <c r="U9" t="n">
-        <v>80</v>
+        <v>80.00505050505051</v>
       </c>
       <c r="V9" t="n">
-        <v>27.12114478114478</v>
+        <v>27.02211589580011</v>
       </c>
       <c r="W9" t="n">
-        <v>182.2076094276094</v>
+        <v>182.0886230728336</v>
       </c>
       <c r="X9" t="n">
-        <v>2.087878787878788</v>
+        <v>2.092716640085061</v>
       </c>
       <c r="Y9" t="n">
-        <v>76.66787878787879</v>
+        <v>76.62785752259435</v>
       </c>
       <c r="Z9" t="n">
-        <v>9858579.124579124</v>
+        <v>9853157.894736841</v>
       </c>
       <c r="AA9" t="n">
-        <v>78.98855218855218</v>
+        <v>79.01632110579479</v>
       </c>
       <c r="AB9" t="n">
-        <v>22.78007936507937</v>
+        <v>22.88617724867725</v>
       </c>
       <c r="AC9" t="n">
-        <v>181.6821957671958</v>
+        <v>181.6518298059965</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.352222222222222</v>
+        <v>1.362962962962963</v>
       </c>
       <c r="AE9" t="n">
-        <v>72.81455026455026</v>
+        <v>72.84545855379189</v>
       </c>
       <c r="AF9" t="n">
-        <v>8036562.169312169</v>
+        <v>7899912.918871252</v>
       </c>
       <c r="AG9" t="n">
-        <v>79.37095238095237</v>
+        <v>79.30912698412698</v>
       </c>
       <c r="AH9" t="n">
-        <v>25.26641509448011</v>
+        <v>25.1227128356589</v>
       </c>
       <c r="AI9" t="n">
-        <v>179.4661061670814</v>
+        <v>179.8160779681637</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.517341176768421</v>
+        <v>1.477349550581586</v>
       </c>
       <c r="AK9" t="n">
-        <v>74.02247401778362</v>
+        <v>74.03142267903551</v>
       </c>
       <c r="AL9" t="n">
-        <v>6346657.154621552</v>
+        <v>6330850.886480673</v>
       </c>
       <c r="AM9" t="n">
-        <v>78.29113477395211</v>
+        <v>78.40183572379678</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -1857,76 +1857,76 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>22.88111888111888</v>
+        <v>22.96969696969697</v>
       </c>
       <c r="Q10" t="n">
-        <v>183.8321678321678</v>
+        <v>183.769696969697</v>
       </c>
       <c r="R10" t="n">
-        <v>1.083916083916084</v>
+        <v>1.084848484848485</v>
       </c>
       <c r="S10" t="n">
-        <v>72.55244755244756</v>
+        <v>72.53939393939395</v>
       </c>
       <c r="T10" t="n">
-        <v>5576923.076923077</v>
+        <v>5523030.303030303</v>
       </c>
       <c r="U10" t="n">
-        <v>79.06993006993008</v>
+        <v>78.92727272727274</v>
       </c>
       <c r="V10" t="n">
-        <v>26.36363636363636</v>
+        <v>26.37575757575758</v>
       </c>
       <c r="W10" t="n">
-        <v>182.7954545454545</v>
+        <v>183.0787878787879</v>
       </c>
       <c r="X10" t="n">
-        <v>1.545454545454545</v>
+        <v>1.539393939393939</v>
       </c>
       <c r="Y10" t="n">
-        <v>73.15909090909092</v>
+        <v>73.07272727272728</v>
       </c>
       <c r="Z10" t="n">
-        <v>4888636.363636364</v>
+        <v>4788181.818181818</v>
       </c>
       <c r="AA10" t="n">
-        <v>75.88636363636364</v>
+        <v>75.87878787878786</v>
       </c>
       <c r="AB10" t="n">
-        <v>22.93296437861655</v>
+        <v>22.84560616517138</v>
       </c>
       <c r="AC10" t="n">
-        <v>180.8736330095026</v>
+        <v>180.7867782378652</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>70.64713064713065</v>
+        <v>70.50899470899471</v>
       </c>
       <c r="AF10" t="n">
-        <v>3625059.05929819</v>
+        <v>3587273.40694732</v>
       </c>
       <c r="AG10" t="n">
-        <v>77.49670860540427</v>
+        <v>77.57862893949851</v>
       </c>
       <c r="AH10" t="n">
-        <v>25.67441953175649</v>
+        <v>25.48292186879143</v>
       </c>
       <c r="AI10" t="n">
-        <v>180.6664242058264</v>
+        <v>180.5774515339733</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.141840898634377</v>
+        <v>1.130403935838718</v>
       </c>
       <c r="AK10" t="n">
-        <v>70.18395262145263</v>
+        <v>69.51316738816739</v>
       </c>
       <c r="AL10" t="n">
-        <v>2461199.671403476</v>
+        <v>2312763.969927013</v>
       </c>
       <c r="AM10" t="n">
-        <v>73.78836305602611</v>
+        <v>73.49166928079971</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>

--- a/p6_deployment/data/france/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/france/data_preparation/df_filled.xlsx
@@ -1146,22 +1146,22 @@
         <v>74.89318181818183</v>
       </c>
       <c r="V5" t="n">
-        <v>24.22017231134878</v>
+        <v>24.25268308080808</v>
       </c>
       <c r="W5" t="n">
-        <v>183.4426322043969</v>
+        <v>183.3952967171717</v>
       </c>
       <c r="X5" t="n">
-        <v>2.365210932857991</v>
+        <v>2.363036616161616</v>
       </c>
       <c r="Y5" t="n">
-        <v>81.60564468211527</v>
+        <v>81.58099747474748</v>
       </c>
       <c r="Z5" t="n">
-        <v>45499509.80392157</v>
+        <v>45152604.16666666</v>
       </c>
       <c r="AA5" t="n">
-        <v>85.4336898395722</v>
+        <v>85.41704545454544</v>
       </c>
       <c r="AB5" t="n">
         <v>24.99190605590062</v>
@@ -1182,22 +1182,22 @@
         <v>72.81624611801243</v>
       </c>
       <c r="AH5" t="n">
-        <v>24.33985321275324</v>
+        <v>24.34286093092208</v>
       </c>
       <c r="AI5" t="n">
-        <v>183.4787622112557</v>
+        <v>183.5450426515635</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.188181787026907</v>
+        <v>2.206572838687132</v>
       </c>
       <c r="AK5" t="n">
-        <v>78.73178644495655</v>
+        <v>78.95498092999384</v>
       </c>
       <c r="AL5" t="n">
-        <v>33333094.78223422</v>
+        <v>34444457.19077105</v>
       </c>
       <c r="AM5" t="n">
-        <v>83.7123453952218</v>
+        <v>83.77572966321031</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1440,22 +1440,22 @@
         <v>77.52840909090909</v>
       </c>
       <c r="V7" t="n">
-        <v>22.37783719548426</v>
+        <v>22.35770202020202</v>
       </c>
       <c r="W7" t="n">
-        <v>183.664468211527</v>
+        <v>183.6309974747475</v>
       </c>
       <c r="X7" t="n">
-        <v>1.19863339275104</v>
+        <v>1.19854797979798</v>
       </c>
       <c r="Y7" t="n">
-        <v>71.73713606654783</v>
+        <v>71.69570707070707</v>
       </c>
       <c r="Z7" t="n">
-        <v>4693030.303030304</v>
+        <v>4655719.696969697</v>
       </c>
       <c r="AA7" t="n">
-        <v>79.22828282828283</v>
+        <v>79.2425505050505</v>
       </c>
       <c r="AB7" t="n">
         <v>23.80568495514148</v>

--- a/p6_deployment/data/france/data_preparation/df_filled.xlsx
+++ b/p6_deployment/data/france/data_preparation/df_filled.xlsx
@@ -697,76 +697,76 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>27.33806818181818</v>
+        <v>26.675</v>
       </c>
       <c r="Q2" t="n">
-        <v>183.2903409090909</v>
+        <v>183.2261363636363</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>69.21534090909091</v>
+        <v>68.77272727272728</v>
       </c>
       <c r="T2" t="n">
-        <v>1655241.477272728</v>
+        <v>1648238.636363636</v>
       </c>
       <c r="U2" t="n">
-        <v>72.13806818181817</v>
+        <v>72.34659090909091</v>
       </c>
       <c r="V2" t="n">
-        <v>26.0969696969697</v>
+        <v>26.62337662337663</v>
       </c>
       <c r="W2" t="n">
-        <v>180.4</v>
+        <v>180.5064935064935</v>
       </c>
       <c r="X2" t="n">
-        <v>1.412121212121213</v>
+        <v>1.402597402597403</v>
       </c>
       <c r="Y2" t="n">
-        <v>76.9939393939394</v>
+        <v>77.05194805194806</v>
       </c>
       <c r="Z2" t="n">
-        <v>13494242.42424243</v>
+        <v>13182467.53246753</v>
       </c>
       <c r="AA2" t="n">
-        <v>79.85454545454546</v>
+        <v>79.42857142857143</v>
       </c>
       <c r="AB2" t="n">
-        <v>24.19276556776557</v>
+        <v>24.5224358974359</v>
       </c>
       <c r="AC2" t="n">
-        <v>182.9535485347986</v>
+        <v>182.5160256410257</v>
       </c>
       <c r="AD2" t="n">
         <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>64.95448717948719</v>
+        <v>65.21314102564102</v>
       </c>
       <c r="AF2" t="n">
-        <v>1100629.006410256</v>
+        <v>1102403.846153846</v>
       </c>
       <c r="AG2" t="n">
-        <v>71.01467490842491</v>
+        <v>70.7603021978022</v>
       </c>
       <c r="AH2" t="n">
-        <v>26.50701058201058</v>
+        <v>26.26303854875284</v>
       </c>
       <c r="AI2" t="n">
-        <v>178.6937830687831</v>
+        <v>177.8795351473923</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.369312169312169</v>
+        <v>1.374716553287982</v>
       </c>
       <c r="AK2" t="n">
-        <v>74.1755291005291</v>
+        <v>74.23526077097506</v>
       </c>
       <c r="AL2" t="n">
-        <v>6571474.867724868</v>
+        <v>6823299.319727891</v>
       </c>
       <c r="AM2" t="n">
-        <v>77.13068783068783</v>
+        <v>77.27607709750566</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
@@ -842,76 +842,76 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>25.89204545454546</v>
+        <v>25.73863636363636</v>
       </c>
       <c r="Q3" t="n">
-        <v>181.3295454545454</v>
+        <v>181.4090909090909</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>68.49431818181819</v>
+        <v>68.65909090909091</v>
       </c>
       <c r="T3" t="n">
-        <v>1682244.318181818</v>
+        <v>1723579.545454545</v>
       </c>
       <c r="U3" t="n">
-        <v>71.33522727272728</v>
+        <v>71.68181818181819</v>
       </c>
       <c r="V3" t="n">
-        <v>23.6524064171123</v>
+        <v>23.4025974025974</v>
       </c>
       <c r="W3" t="n">
-        <v>183.3689839572192</v>
+        <v>183.9090909090909</v>
       </c>
       <c r="X3" t="n">
-        <v>1.32620320855615</v>
+        <v>1.324675324675325</v>
       </c>
       <c r="Y3" t="n">
-        <v>75.24064171122994</v>
+        <v>75.22077922077922</v>
       </c>
       <c r="Z3" t="n">
-        <v>12514973.26203208</v>
+        <v>12789610.38961039</v>
       </c>
       <c r="AA3" t="n">
-        <v>79.89304812834224</v>
+        <v>80.14285714285714</v>
       </c>
       <c r="AB3" t="n">
-        <v>23.14935064935065</v>
+        <v>23.53084415584416</v>
       </c>
       <c r="AC3" t="n">
-        <v>181.0645292207792</v>
+        <v>180.0397727272727</v>
       </c>
       <c r="AD3" t="n">
         <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>65.02962662337663</v>
+        <v>65.61282467532467</v>
       </c>
       <c r="AF3" t="n">
-        <v>1364285.714285714</v>
+        <v>1428571.428571428</v>
       </c>
       <c r="AG3" t="n">
-        <v>71.91233766233766</v>
+        <v>71.59253246753246</v>
       </c>
       <c r="AH3" t="n">
-        <v>23.68470809376382</v>
+        <v>23.94886024585272</v>
       </c>
       <c r="AI3" t="n">
-        <v>180.2043220797091</v>
+        <v>180.7263694951665</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.248384441495897</v>
+        <v>1.325725026852847</v>
       </c>
       <c r="AK3" t="n">
-        <v>73.14841024128951</v>
+        <v>74.00951784222461</v>
       </c>
       <c r="AL3" t="n">
-        <v>6588942.331318492</v>
+        <v>7708321.398734934</v>
       </c>
       <c r="AM3" t="n">
-        <v>78.19739299228463</v>
+        <v>78.50404284520826</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -987,76 +987,76 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>26.35227272727273</v>
+        <v>26.41558441558442</v>
       </c>
       <c r="Q4" t="n">
-        <v>181.7045454545455</v>
+        <v>182</v>
       </c>
       <c r="R4" t="n">
-        <v>1.301136363636364</v>
+        <v>1.337662337662338</v>
       </c>
       <c r="S4" t="n">
-        <v>74.93181818181817</v>
+        <v>74.96103896103897</v>
       </c>
       <c r="T4" t="n">
-        <v>7138068.181818182</v>
+        <v>6997402.597402598</v>
       </c>
       <c r="U4" t="n">
-        <v>77.25568181818181</v>
+        <v>77.28571428571429</v>
       </c>
       <c r="V4" t="n">
-        <v>26.55090909090909</v>
+        <v>26.92077922077922</v>
       </c>
       <c r="W4" t="n">
-        <v>183.569696969697</v>
+        <v>183.9012987012987</v>
       </c>
       <c r="X4" t="n">
-        <v>1.669090909090909</v>
+        <v>1.693506493506494</v>
       </c>
       <c r="Y4" t="n">
-        <v>77.11999999999999</v>
+        <v>77.19740259740261</v>
       </c>
       <c r="Z4" t="n">
-        <v>12317454.54545454</v>
+        <v>12364285.71428571</v>
       </c>
       <c r="AA4" t="n">
-        <v>79.40363636363637</v>
+        <v>79.19350649350648</v>
       </c>
       <c r="AB4" t="n">
-        <v>23.87743055555556</v>
+        <v>24.55317460317461</v>
       </c>
       <c r="AC4" t="n">
-        <v>179.8616319444445</v>
+        <v>179.9674603174603</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.143253968253968</v>
+        <v>1.132993197278912</v>
       </c>
       <c r="AE4" t="n">
-        <v>69.12792658730157</v>
+        <v>70.91145124716554</v>
       </c>
       <c r="AF4" t="n">
-        <v>3391687.12797619</v>
+        <v>4394342.403628118</v>
       </c>
       <c r="AG4" t="n">
-        <v>74.08876488095238</v>
+        <v>74.68503401360545</v>
       </c>
       <c r="AH4" t="n">
-        <v>24.74450054875751</v>
+        <v>25.05369165209944</v>
       </c>
       <c r="AI4" t="n">
-        <v>184.1523513030943</v>
+        <v>184.0475555134335</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.195205333595427</v>
+        <v>1.260133878112649</v>
       </c>
       <c r="AK4" t="n">
-        <v>74.1863454387603</v>
+        <v>75.1578150558469</v>
       </c>
       <c r="AL4" t="n">
-        <v>8210018.407947974</v>
+        <v>9768109.173493957</v>
       </c>
       <c r="AM4" t="n">
-        <v>77.8814130915524</v>
+        <v>78.55966070638782</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
@@ -1128,76 +1128,76 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>25.36590909090909</v>
+        <v>25.25064935064935</v>
       </c>
       <c r="Q5" t="n">
-        <v>185.7704545454546</v>
+        <v>185.8441558441559</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>71.50170454545454</v>
+        <v>71.51818181818182</v>
       </c>
       <c r="T5" t="n">
-        <v>3006875</v>
+        <v>3005714.285714286</v>
       </c>
       <c r="U5" t="n">
-        <v>74.89318181818183</v>
+        <v>74.96883116883116</v>
       </c>
       <c r="V5" t="n">
-        <v>24.25268308080808</v>
+        <v>24.27175925925926</v>
       </c>
       <c r="W5" t="n">
-        <v>183.3952967171717</v>
+        <v>183.4763888888889</v>
       </c>
       <c r="X5" t="n">
-        <v>2.363036616161616</v>
+        <v>2.216666666666666</v>
       </c>
       <c r="Y5" t="n">
-        <v>81.58099747474748</v>
+        <v>80.28842592592594</v>
       </c>
       <c r="Z5" t="n">
-        <v>45152604.16666666</v>
+        <v>36460648.14814814</v>
       </c>
       <c r="AA5" t="n">
-        <v>85.41704545454544</v>
+        <v>84.63796296296296</v>
       </c>
       <c r="AB5" t="n">
-        <v>24.99190605590062</v>
+        <v>25.1303090801538</v>
       </c>
       <c r="AC5" t="n">
-        <v>181.4308477829538</v>
+        <v>181.4213028689737</v>
       </c>
       <c r="AD5" t="n">
         <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>68.52984601449276</v>
+        <v>69.2725845410628</v>
       </c>
       <c r="AF5" t="n">
-        <v>1906706.591830573</v>
+        <v>2262303.559104801</v>
       </c>
       <c r="AG5" t="n">
-        <v>72.81624611801243</v>
+        <v>73.17126096815538</v>
       </c>
       <c r="AH5" t="n">
-        <v>24.34286093092208</v>
+        <v>23.78706209457467</v>
       </c>
       <c r="AI5" t="n">
-        <v>183.5450426515635</v>
+        <v>183.4086376326846</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.206572838687132</v>
+        <v>2.233638093395253</v>
       </c>
       <c r="AK5" t="n">
-        <v>78.95498092999384</v>
+        <v>78.39821106074008</v>
       </c>
       <c r="AL5" t="n">
-        <v>34444457.19077105</v>
+        <v>36262156.65542533</v>
       </c>
       <c r="AM5" t="n">
-        <v>83.77572966321031</v>
+        <v>83.81905245650893</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1273,76 +1273,76 @@
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>24.65347222222222</v>
+        <v>24.41443001443001</v>
       </c>
       <c r="Q6" t="n">
-        <v>182.5606691919192</v>
+        <v>182.132178932179</v>
       </c>
       <c r="R6" t="n">
-        <v>1.606186868686869</v>
+        <v>1.551803751803752</v>
       </c>
       <c r="S6" t="n">
-        <v>76.99135101010101</v>
+        <v>76.88282828282829</v>
       </c>
       <c r="T6" t="n">
-        <v>15180366.16161616</v>
+        <v>14999278.4992785</v>
       </c>
       <c r="U6" t="n">
-        <v>81.32891414141415</v>
+        <v>81.45569985569986</v>
       </c>
       <c r="V6" t="n">
-        <v>25.78086124401914</v>
+        <v>25.54049586776859</v>
       </c>
       <c r="W6" t="n">
-        <v>181.321052631579</v>
+        <v>181.4157024793388</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>70.50382775119617</v>
+        <v>70.31239669421488</v>
       </c>
       <c r="Z6" t="n">
-        <v>2267057.416267943</v>
+        <v>2263388.429752066</v>
       </c>
       <c r="AA6" t="n">
-        <v>73.78229665071771</v>
+        <v>73.8396694214876</v>
       </c>
       <c r="AB6" t="n">
-        <v>21.65601148354079</v>
+        <v>22.57919983782987</v>
       </c>
       <c r="AC6" t="n">
-        <v>181.1161111813146</v>
+        <v>181.2851135190919</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.199589309407974</v>
+        <v>1.343056169836355</v>
       </c>
       <c r="AE6" t="n">
-        <v>73.49054213790779</v>
+        <v>74.85098223499926</v>
       </c>
       <c r="AF6" t="n">
-        <v>9508926.044101851</v>
+        <v>11684246.64602683</v>
       </c>
       <c r="AG6" t="n">
-        <v>81.62886404561824</v>
+        <v>81.53119747899159</v>
       </c>
       <c r="AH6" t="n">
-        <v>24.47315549947129</v>
+        <v>25.07700884973612</v>
       </c>
       <c r="AI6" t="n">
-        <v>180.3457653457653</v>
+        <v>180.2076206621661</v>
       </c>
       <c r="AJ6" t="n">
         <v>1</v>
       </c>
       <c r="AK6" t="n">
-        <v>68.51232685443212</v>
+        <v>68.94986326804509</v>
       </c>
       <c r="AL6" t="n">
-        <v>1912655.4001554</v>
+        <v>1933114.738796557</v>
       </c>
       <c r="AM6" t="n">
-        <v>73.88977396872133</v>
+        <v>73.63212040484768</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
@@ -1422,76 +1422,76 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>25.45681818181818</v>
+        <v>24.68831168831169</v>
       </c>
       <c r="Q7" t="n">
-        <v>181.4426136363637</v>
+        <v>182.1181818181819</v>
       </c>
       <c r="R7" t="n">
-        <v>1.355681818181818</v>
+        <v>1.319480519480519</v>
       </c>
       <c r="S7" t="n">
-        <v>73.2590909090909</v>
+        <v>72.90259740259741</v>
       </c>
       <c r="T7" t="n">
-        <v>5430227.272727272</v>
+        <v>5346753.246753247</v>
       </c>
       <c r="U7" t="n">
-        <v>77.52840909090909</v>
+        <v>77.89740259740259</v>
       </c>
       <c r="V7" t="n">
-        <v>22.35770202020202</v>
+        <v>22.18253968253968</v>
       </c>
       <c r="W7" t="n">
-        <v>183.6309974747475</v>
+        <v>183.0682539682539</v>
       </c>
       <c r="X7" t="n">
-        <v>1.19854797979798</v>
+        <v>1.188888888888889</v>
       </c>
       <c r="Y7" t="n">
-        <v>71.69570707070707</v>
+        <v>71.36031746031746</v>
       </c>
       <c r="Z7" t="n">
-        <v>4655719.696969697</v>
+        <v>4507619.047619048</v>
       </c>
       <c r="AA7" t="n">
-        <v>79.2425505050505</v>
+        <v>79.39206349206349</v>
       </c>
       <c r="AB7" t="n">
-        <v>23.80568495514148</v>
+        <v>24.52467218771566</v>
       </c>
       <c r="AC7" t="n">
-        <v>181.5474971963423</v>
+        <v>181.467692004338</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.145726578674948</v>
+        <v>1.185980479148181</v>
       </c>
       <c r="AE7" t="n">
-        <v>70.33750107832988</v>
+        <v>71.12885734003746</v>
       </c>
       <c r="AF7" t="n">
-        <v>3326543.1978951</v>
+        <v>3666877.649610569</v>
       </c>
       <c r="AG7" t="n">
-        <v>76.11016865079365</v>
+        <v>76.03582766439909</v>
       </c>
       <c r="AH7" t="n">
-        <v>23.51894578344158</v>
+        <v>23.54197319953623</v>
       </c>
       <c r="AI7" t="n">
-        <v>182.6658432603811</v>
+        <v>182.5731831194016</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.250674115800166</v>
+        <v>1.271416258811217</v>
       </c>
       <c r="AK7" t="n">
-        <v>69.3217666553801</v>
+        <v>70.46462174613436</v>
       </c>
       <c r="AL7" t="n">
-        <v>3029012.50756713</v>
+        <v>3528691.681800925</v>
       </c>
       <c r="AM7" t="n">
-        <v>76.637002493305</v>
+        <v>77.16448117708622</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
@@ -1567,76 +1567,76 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>25.81239316239316</v>
+        <v>25.59888888888889</v>
       </c>
       <c r="Q8" t="n">
-        <v>182.642735042735</v>
+        <v>182.9111111111111</v>
       </c>
       <c r="R8" t="n">
-        <v>1.236965811965812</v>
+        <v>1.253888888888889</v>
       </c>
       <c r="S8" t="n">
-        <v>74.57713675213675</v>
+        <v>74.38500000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>7714481.837606838</v>
+        <v>7680597.222222222</v>
       </c>
       <c r="U8" t="n">
-        <v>78.6707264957265</v>
+        <v>78.91055555555556</v>
       </c>
       <c r="V8" t="n">
-        <v>24.14545454545454</v>
+        <v>24.38701298701298</v>
       </c>
       <c r="W8" t="n">
-        <v>180.5926136363636</v>
+        <v>180.5090909090909</v>
       </c>
       <c r="X8" t="n">
-        <v>1.466477272727273</v>
+        <v>1.472727272727273</v>
       </c>
       <c r="Y8" t="n">
-        <v>76.64204545454545</v>
+        <v>76.60649350649351</v>
       </c>
       <c r="Z8" t="n">
-        <v>13325000</v>
+        <v>13120000</v>
       </c>
       <c r="AA8" t="n">
-        <v>81.34488636363636</v>
+        <v>81.32597402597402</v>
       </c>
       <c r="AB8" t="n">
-        <v>22.59129211918685</v>
+        <v>22.85038787444802</v>
       </c>
       <c r="AC8" t="n">
-        <v>183.5230882762462</v>
+        <v>183.5035565103234</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.068720412141465</v>
+        <v>1.07327843418069</v>
       </c>
       <c r="AE8" t="n">
-        <v>69.00193539404066</v>
+        <v>69.28816087838644</v>
       </c>
       <c r="AF8" t="n">
-        <v>3671667.362851573</v>
+        <v>3911140.947607113</v>
       </c>
       <c r="AG8" t="n">
-        <v>77.42074631022</v>
+        <v>77.34037474638978</v>
       </c>
       <c r="AH8" t="n">
-        <v>25.54852576151918</v>
+        <v>25.77928337326833</v>
       </c>
       <c r="AI8" t="n">
-        <v>181.3932357938115</v>
+        <v>180.5302872566031</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.197837743396954</v>
+        <v>1.200840012118207</v>
       </c>
       <c r="AK8" t="n">
-        <v>72.1042949922884</v>
+        <v>73.57410283951637</v>
       </c>
       <c r="AL8" t="n">
-        <v>5491748.790546076</v>
+        <v>7146739.582472665</v>
       </c>
       <c r="AM8" t="n">
-        <v>77.23226847165992</v>
+        <v>77.84603541821586</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
@@ -1712,76 +1712,76 @@
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>24.40909090909091</v>
+        <v>24.28571428571428</v>
       </c>
       <c r="Q9" t="n">
-        <v>181.6010101010101</v>
+        <v>181.1688311688312</v>
       </c>
       <c r="R9" t="n">
-        <v>1.681818181818181</v>
+        <v>1.688311688311688</v>
       </c>
       <c r="S9" t="n">
-        <v>75.80303030303031</v>
+        <v>75.8961038961039</v>
       </c>
       <c r="T9" t="n">
-        <v>10589898.98989899</v>
+        <v>10606493.50649351</v>
       </c>
       <c r="U9" t="n">
-        <v>80.00505050505051</v>
+        <v>80.2987012987013</v>
       </c>
       <c r="V9" t="n">
-        <v>27.02211589580011</v>
+        <v>27.33080808080808</v>
       </c>
       <c r="W9" t="n">
-        <v>182.0886230728336</v>
+        <v>181.9578282828283</v>
       </c>
       <c r="X9" t="n">
-        <v>2.092716640085061</v>
+        <v>2.113131313131313</v>
       </c>
       <c r="Y9" t="n">
-        <v>76.62785752259435</v>
+        <v>76.76376262626263</v>
       </c>
       <c r="Z9" t="n">
-        <v>9853157.894736841</v>
+        <v>9961792.929292928</v>
       </c>
       <c r="AA9" t="n">
-        <v>79.01632110579479</v>
+        <v>78.93901515151515</v>
       </c>
       <c r="AB9" t="n">
-        <v>22.88617724867725</v>
+        <v>23.00918367346939</v>
       </c>
       <c r="AC9" t="n">
-        <v>181.6518298059965</v>
+        <v>181.2886621315193</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.362962962962963</v>
+        <v>1.438151927437642</v>
       </c>
       <c r="AE9" t="n">
-        <v>72.84545855379189</v>
+        <v>74.08475056689342</v>
       </c>
       <c r="AF9" t="n">
-        <v>7899912.918871252</v>
+        <v>9713390.022675736</v>
       </c>
       <c r="AG9" t="n">
-        <v>79.30912698412698</v>
+        <v>79.74359410430839</v>
       </c>
       <c r="AH9" t="n">
-        <v>25.1227128356589</v>
+        <v>25.10195885770576</v>
       </c>
       <c r="AI9" t="n">
-        <v>179.8160779681637</v>
+        <v>178.6847129521665</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.477349550581586</v>
+        <v>1.572941293742377</v>
       </c>
       <c r="AK9" t="n">
-        <v>74.03142267903551</v>
+        <v>74.35191060874109</v>
       </c>
       <c r="AL9" t="n">
-        <v>6330850.886480673</v>
+        <v>7151296.649042392</v>
       </c>
       <c r="AM9" t="n">
-        <v>78.40183572379678</v>
+        <v>78.74329833608084</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -1857,76 +1857,76 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>22.96969696969697</v>
+        <v>23.06493506493506</v>
       </c>
       <c r="Q10" t="n">
-        <v>183.769696969697</v>
+        <v>183.8441558441559</v>
       </c>
       <c r="R10" t="n">
-        <v>1.084848484848485</v>
+        <v>1.077922077922078</v>
       </c>
       <c r="S10" t="n">
-        <v>72.53939393939395</v>
+        <v>72.81818181818183</v>
       </c>
       <c r="T10" t="n">
-        <v>5523030.303030303</v>
+        <v>5758441.558441558</v>
       </c>
       <c r="U10" t="n">
-        <v>78.92727272727274</v>
+        <v>78.98701298701299</v>
       </c>
       <c r="V10" t="n">
-        <v>26.37575757575758</v>
+        <v>26.48051948051948</v>
       </c>
       <c r="W10" t="n">
-        <v>183.0787878787879</v>
+        <v>183.1298701298701</v>
       </c>
       <c r="X10" t="n">
-        <v>1.539393939393939</v>
+        <v>1.519480519480519</v>
       </c>
       <c r="Y10" t="n">
-        <v>73.07272727272728</v>
+        <v>72.81818181818183</v>
       </c>
       <c r="Z10" t="n">
-        <v>4788181.818181818</v>
+        <v>4483766.233766234</v>
       </c>
       <c r="AA10" t="n">
-        <v>75.87878787878786</v>
+        <v>75.46753246753246</v>
       </c>
       <c r="AB10" t="n">
-        <v>22.84560616517138</v>
+        <v>23.06598146504978</v>
       </c>
       <c r="AC10" t="n">
-        <v>180.7867782378652</v>
+        <v>180.9081755890762</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>70.50899470899471</v>
+        <v>70.93197278911565</v>
       </c>
       <c r="AF10" t="n">
-        <v>3587273.40694732</v>
+        <v>3747331.903776004</v>
       </c>
       <c r="AG10" t="n">
-        <v>77.57862893949851</v>
+        <v>77.44626836241743</v>
       </c>
       <c r="AH10" t="n">
-        <v>25.48292186879143</v>
+        <v>25.64821126078891</v>
       </c>
       <c r="AI10" t="n">
-        <v>180.5774515339733</v>
+        <v>180.1106954639563</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.130403935838718</v>
+        <v>1.147917730992265</v>
       </c>
       <c r="AK10" t="n">
-        <v>69.51316738816739</v>
+        <v>70.20423623995053</v>
       </c>
       <c r="AL10" t="n">
-        <v>2312763.969927013</v>
+        <v>2599596.262088499</v>
       </c>
       <c r="AM10" t="n">
-        <v>73.49166928079971</v>
+        <v>73.8911620642987</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
